--- a/FightingRush.xlsx
+++ b/FightingRush.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7353AFF-DE56-4C9A-A9EC-CFCCD6A4E20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1159139D-680A-47B0-8A02-40863BF45B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -321,9 +321,6 @@
   </si>
   <si>
     <t>　ー　エフェクト再生</t>
-  </si>
-  <si>
-    <t>　ー　エフェクト停止</t>
   </si>
   <si>
     <t>　ー　エフェクト実装</t>
@@ -741,8 +738,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E43" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E43" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E42" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E42" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1013,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1034,7 +1031,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
@@ -1049,8 +1046,8 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C43)</f>
-        <v>127</v>
+        <f>SUM(C3:C42)</f>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1064,14 +1061,14 @@
         <v>1</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E43,"完了",C3:C43)</f>
-        <v>126</v>
+        <f>SUMIF(E3:E42,"完了",C3:C42)</f>
+        <v>133</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -1091,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>10</v>
@@ -1105,7 +1102,7 @@
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>6</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
@@ -1113,12 +1110,12 @@
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>4.2</v>
+        <v>4.4333333333333336</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C5" s="8">
         <f>SUM(C6:C10)</f>
@@ -1126,7 +1123,7 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>12</v>
@@ -1147,7 +1144,7 @@
         <v>1</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>14</v>
@@ -1164,9 +1161,11 @@
       <c r="C7" s="7">
         <v>0.5</v>
       </c>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7">
+        <v>1</v>
+      </c>
       <c r="E7" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1176,9 +1175,11 @@
       <c r="C8" s="7">
         <v>0.5</v>
       </c>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
       <c r="E8" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1188,9 +1189,11 @@
       <c r="C9" s="7">
         <v>0.5</v>
       </c>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7">
+        <v>1</v>
+      </c>
       <c r="E9" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1200,14 +1203,16 @@
       <c r="C10" s="7">
         <v>0.5</v>
       </c>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
       <c r="E10" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C11" s="8">
         <f>SUM(C12:C21)</f>
@@ -1217,7 +1222,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
@@ -1243,7 +1248,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>23</v>
@@ -1258,7 +1263,7 @@
       </c>
       <c r="J12" s="3">
         <f ca="1">($H$2 - $H$3) / I12</f>
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="K12">
         <f ca="1">_xlfn.DAYS(H12,$H$6)</f>
@@ -1266,12 +1271,12 @@
       </c>
       <c r="L12" s="3">
         <f ca="1">($H$2 - $H$3) / K12</f>
-        <v>0.25</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="7">
         <v>6</v>
@@ -1280,7 +1285,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>24</v>
@@ -1295,7 +1300,7 @@
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" ca="1" si="1">_xlfn.DAYS(H13,$H$6)</f>
@@ -1303,12 +1308,12 @@
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>0.16666666666666666</v>
+        <v>1.3333333333333333</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="7">
         <v>3</v>
@@ -1317,7 +1322,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>25</v>
@@ -1332,7 +1337,7 @@
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>-5.235602094240838E-3</v>
+        <v>-4.1884816753926704E-2</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="1"/>
@@ -1340,12 +1345,12 @@
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>-3.7453183520599251E-3</v>
+        <v>-2.9962546816479401E-2</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15" s="7">
         <v>3</v>
@@ -1354,12 +1359,12 @@
         <v>2</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
@@ -1368,12 +1373,12 @@
         <v>2</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="7">
         <v>2</v>
@@ -1382,12 +1387,12 @@
         <v>1</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C18" s="7">
         <v>3</v>
@@ -1396,12 +1401,12 @@
         <v>2</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19" s="7">
         <v>2</v>
@@ -1410,7 +1415,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -1424,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1438,12 +1443,12 @@
         <v>3</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C22" s="8">
         <v>12</v>
@@ -1452,12 +1457,12 @@
         <v>10</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C23" s="7">
         <v>10</v>
@@ -1466,12 +1471,12 @@
         <v>8</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C24" s="7">
         <v>2</v>
@@ -1480,7 +1485,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1494,7 +1499,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -1508,7 +1513,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1522,47 +1527,61 @@
         <v>6</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="2:5">
       <c r="B28" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
+      <c r="C28" s="8">
+        <v>5</v>
+      </c>
+      <c r="D28" s="8">
+        <v>5</v>
+      </c>
       <c r="E28" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="2:5">
       <c r="B29" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
+      <c r="C29" s="7">
+        <v>2</v>
+      </c>
+      <c r="D29" s="7">
+        <v>2</v>
+      </c>
       <c r="E29" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="2:5">
       <c r="B30" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
+      <c r="C30" s="7">
+        <v>2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>2</v>
+      </c>
       <c r="E30" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="2:5">
       <c r="B31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="7"/>
+      <c r="C31" s="7">
+        <v>1</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -1576,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33" spans="2:5">
@@ -1590,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="34" spans="2:5">
@@ -1604,12 +1623,12 @@
         <v>1</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -1618,12 +1637,12 @@
         <v>0.5</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C36" s="7">
         <v>1</v>
@@ -1632,7 +1651,7 @@
         <v>0.5</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="2:5">
@@ -1646,7 +1665,7 @@
         <v>2</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="38" spans="2:5">
@@ -1660,61 +1679,63 @@
         <v>2</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="2:5">
       <c r="B39" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
+      <c r="C39" s="8">
+        <v>2</v>
+      </c>
+      <c r="D39" s="8">
+        <v>2</v>
+      </c>
       <c r="E39" s="17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
+      <c r="C40" s="7">
+        <v>1</v>
+      </c>
+      <c r="D40" s="7">
+        <v>1</v>
+      </c>
       <c r="E40" s="16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41" spans="2:5">
       <c r="B41" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="16" t="s">
-        <v>57</v>
+      <c r="C41" s="7">
+        <v>1</v>
+      </c>
+      <c r="D41" s="7">
+        <v>1</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="7" t="s">
+      <c r="B42" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="19" t="s">
-        <v>57</v>
+      <c r="C42" s="8"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C43" s="8"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="8" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="D44" s="15"/>
+      <c r="D43" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1747,26 +1768,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -2001,10 +2002,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2021,20 +2053,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/FightingRush.xlsx
+++ b/FightingRush.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\NatuSakuhin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1159139D-680A-47B0-8A02-40863BF45B96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026DB416-F215-44A3-8FA4-D2776D851630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -330,10 +330,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>プロト</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>・プロト素材集め</t>
     <rPh sb="4" eb="6">
       <t>ソザイ</t>
@@ -427,6 +423,17 @@
     <rPh sb="8" eb="10">
       <t>ツイジュウ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>全体</t>
+    <rPh sb="0" eb="2">
+      <t>ゼンタイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー 　クリアタイム</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -738,8 +745,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E42" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E42" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E44" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E44" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1010,7 +1017,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1031,7 +1038,7 @@
     </row>
     <row r="2" spans="1:12">
       <c r="B2" s="4" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>1</v>
@@ -1046,8 +1053,8 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C42)</f>
-        <v>141</v>
+        <f>SUM(C3:C44)</f>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1061,14 +1068,14 @@
         <v>1</v>
       </c>
       <c r="E3" s="17" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E42,"完了",C3:C42)</f>
-        <v>133</v>
+        <f>SUMIF(E3:E44,"完了",C3:C44)</f>
+        <v>142</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -1088,34 +1095,34 @@
         <v>1</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4" s="11" t="s">
         <v>10</v>
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>6.333333333333333</v>
+        <v>6.1739130434782608</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>4.4333333333333336</v>
+        <v>4.4375</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="B5" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="8">
         <f>SUM(C6:C10)</f>
@@ -1123,7 +1130,7 @@
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G5" s="12" t="s">
         <v>12</v>
@@ -1144,14 +1151,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>14</v>
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46258</v>
+        <v>46260</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1165,7 +1172,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1179,7 +1186,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1193,7 +1200,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1207,12 +1214,12 @@
         <v>1</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="B11" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="8">
         <f>SUM(C12:C21)</f>
@@ -1222,7 +1229,7 @@
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
@@ -1248,7 +1255,7 @@
         <v>3</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>23</v>
@@ -1259,24 +1266,24 @@
       </c>
       <c r="I12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H12)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J12" s="3">
         <f ca="1">($H$2 - $H$3) / I12</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <f ca="1">_xlfn.DAYS(H12,$H$6)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L12" s="3">
         <f ca="1">($H$2 - $H$3) / K12</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C13" s="7">
         <v>6</v>
@@ -1285,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>24</v>
@@ -1296,24 +1303,24 @@
       </c>
       <c r="I13" s="2">
         <f t="shared" ref="I13:I14" ca="1" si="0">NETWORKDAYS(TODAY(),H13)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" ca="1" si="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
-        <v>1.3333333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="B14" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C14" s="7">
         <v>3</v>
@@ -1322,35 +1329,35 @@
         <v>2</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G14" s="11" t="s">
         <v>25</v>
       </c>
       <c r="H14" s="1">
-        <f>DATE(2026,,)</f>
-        <v>45991</v>
+        <f>DATE(2026,8,31)</f>
+        <v>46265</v>
       </c>
       <c r="I14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>-191</v>
+        <v>4</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
-        <v>-4.1884816753926704E-2</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="1"/>
-        <v>-267</v>
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
-        <v>-2.9962546816479401E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="B15" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="7">
         <v>3</v>
@@ -1359,12 +1366,12 @@
         <v>2</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="B16" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C16" s="7">
         <v>3</v>
@@ -1373,12 +1380,12 @@
         <v>2</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="2:5">
       <c r="B17" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C17" s="7">
         <v>2</v>
@@ -1387,12 +1394,12 @@
         <v>1</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="2:5">
       <c r="B18" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C18" s="7">
         <v>3</v>
@@ -1401,12 +1408,12 @@
         <v>2</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19" spans="2:5">
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C19" s="7">
         <v>2</v>
@@ -1415,7 +1422,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20" spans="2:5">
@@ -1429,7 +1436,7 @@
         <v>2</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="21" spans="2:5">
@@ -1443,12 +1450,12 @@
         <v>3</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="2:5">
       <c r="B22" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C22" s="8">
         <v>12</v>
@@ -1457,12 +1464,12 @@
         <v>10</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23" spans="2:5">
       <c r="B23" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C23" s="7">
         <v>10</v>
@@ -1471,12 +1478,12 @@
         <v>8</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" spans="2:5">
       <c r="B24" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C24" s="7">
         <v>2</v>
@@ -1485,7 +1492,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" spans="2:5">
@@ -1499,7 +1506,7 @@
         <v>12</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="26" spans="2:5">
@@ -1513,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="2:5">
@@ -1527,7 +1534,7 @@
         <v>6</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28" spans="2:5">
@@ -1541,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="2:5">
@@ -1555,7 +1562,7 @@
         <v>2</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="2:5">
@@ -1569,7 +1576,7 @@
         <v>2</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="2:5">
@@ -1579,9 +1586,11 @@
       <c r="C31" s="7">
         <v>1</v>
       </c>
-      <c r="D31" s="7"/>
+      <c r="D31" s="7">
+        <v>1</v>
+      </c>
       <c r="E31" s="16" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="2:5">
@@ -1595,7 +1604,7 @@
         <v>7</v>
       </c>
       <c r="E32" s="17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="33" spans="2:5">
@@ -1609,7 +1618,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="34" spans="2:5">
@@ -1623,12 +1632,12 @@
         <v>1</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="35" spans="2:5">
       <c r="B35" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="7">
         <v>1</v>
@@ -1637,105 +1646,133 @@
         <v>0.5</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="36" spans="2:5">
       <c r="B36" s="7" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C36" s="7">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D36" s="7">
         <v>0.5</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37" spans="2:5">
       <c r="B37" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="7">
+        <v>1</v>
+      </c>
+      <c r="D37" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C37" s="7">
-        <v>1</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2</v>
-      </c>
-      <c r="E37" s="16" t="s">
+      <c r="C38" s="7">
+        <v>1</v>
+      </c>
+      <c r="D38" s="7">
+        <v>2</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5">
+      <c r="B39" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C39" s="21">
+        <v>2</v>
+      </c>
+      <c r="D39" s="21">
+        <v>2</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C40" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="D40" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="8">
+        <v>2</v>
+      </c>
+      <c r="D41" s="8">
+        <v>2</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="7">
+        <v>1</v>
+      </c>
+      <c r="D42" s="7">
+        <v>1</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1</v>
+      </c>
+      <c r="E43" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44" s="8"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="2:5">
-      <c r="B38" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="21">
-        <v>2</v>
-      </c>
-      <c r="D38" s="21">
-        <v>2</v>
-      </c>
-      <c r="E38" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="2:5">
-      <c r="B39" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="8">
-        <v>2</v>
-      </c>
-      <c r="D39" s="8">
-        <v>2</v>
-      </c>
-      <c r="E39" s="17" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="2:5">
-      <c r="B40" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C40" s="7">
-        <v>1</v>
-      </c>
-      <c r="D40" s="7">
-        <v>1</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="2:5">
-      <c r="B41" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C41" s="7">
-        <v>1</v>
-      </c>
-      <c r="D41" s="7">
-        <v>1</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="C42" s="8"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="43" spans="2:5">
-      <c r="D43" s="15"/>
+    <row r="45" spans="2:5">
+      <c r="D45" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1768,6 +1805,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -2002,27 +2059,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2039,23 +2095,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CD2B120-A90D-496C-8884-A2A9574072D6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/FightingRush.xlsx
+++ b/FightingRush.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TeraoAyato\Documents\GitHub\NatuSakuhin\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Train\Documents\GitHub\NatuSakuhin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{026DB416-F215-44A3-8FA4-D2776D851630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A028F5-1C8B-4C1A-8D32-503743065D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="64">
   <si>
     <t>1コスト:3時間 (1日は基本2コスト)</t>
   </si>
@@ -434,6 +434,17 @@
   </si>
   <si>
     <t>　ー 　クリアタイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　タイム</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>　ー　操作方法</t>
+    <rPh sb="3" eb="7">
+      <t>ソウサホウホウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -745,8 +756,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E44" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
-  <autoFilter ref="E2:E44" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}" name="テーブル1" displayName="テーブル1" ref="E2:E45" totalsRowShown="0" headerRowDxfId="5" dataDxfId="3" headerRowBorderDxfId="4" tableBorderDxfId="2" totalsRowBorderDxfId="1">
+  <autoFilter ref="E2:E45" xr:uid="{E042A6E7-930F-48C1-8255-0961B3F4D24F}"/>
   <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{A47BB3CB-D1EF-4B37-9B3E-3ED069040864}" name="判定" dataDxfId="0"/>
   </tableColumns>
@@ -1017,7 +1028,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="9.25" customWidth="1"/>
@@ -1053,8 +1064,8 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <f>SUM(C3:C44)</f>
-        <v>142</v>
+        <f>SUM(C3:C45)</f>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1074,8 +1085,8 @@
         <v>6</v>
       </c>
       <c r="H3">
-        <f>SUMIF(E3:E44,"完了",C3:C44)</f>
-        <v>142</v>
+        <f>SUMIF(E3:E45,"完了",C3:C45)</f>
+        <v>149</v>
       </c>
       <c r="K3" t="s">
         <v>7</v>
@@ -1102,22 +1113,22 @@
       </c>
       <c r="H4" s="2">
         <f ca="1">NETWORKDAYS(H5,H6)</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="3">
         <f ca="1" xml:space="preserve"> H3 / H4</f>
-        <v>6.1739130434782608</v>
+        <v>5.96</v>
       </c>
       <c r="K4" s="2">
         <f ca="1">_xlfn.DAYS(H6,H5)</f>
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="L4" s="3">
         <f ca="1">H3/K4</f>
-        <v>4.4375</v>
+        <v>4.382352941176471</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1128,7 +1139,10 @@
         <f>SUM(C6:C10)</f>
         <v>3</v>
       </c>
-      <c r="D5" s="8"/>
+      <c r="D5" s="8">
+        <f>SUM(D6:D10)</f>
+        <v>5</v>
+      </c>
       <c r="E5" s="17" t="s">
         <v>54</v>
       </c>
@@ -1158,7 +1172,7 @@
       </c>
       <c r="H6" s="1">
         <f ca="1">TODAY()</f>
-        <v>46260</v>
+        <v>46262</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1226,6 +1240,7 @@
         <v>30</v>
       </c>
       <c r="D11" s="8">
+        <f>SUM(D12:D21)</f>
         <v>28</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -1266,7 +1281,7 @@
       </c>
       <c r="I12" s="2">
         <f ca="1">NETWORKDAYS(TODAY(),H12)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J12" s="3">
         <f ca="1">($H$2 - $H$3) / I12</f>
@@ -1274,11 +1289,11 @@
       </c>
       <c r="K12">
         <f ca="1">_xlfn.DAYS(H12,$H$6)</f>
-        <v>2</v>
-      </c>
-      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="e">
         <f ca="1">($H$2 - $H$3) / K12</f>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1303,7 +1318,7 @@
       </c>
       <c r="I13" s="2">
         <f t="shared" ref="I13:I14" ca="1" si="0">NETWORKDAYS(TODAY(),H13)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J13" s="3">
         <f ca="1">($H$2 - $H$3) / I13</f>
@@ -1311,7 +1326,7 @@
       </c>
       <c r="K13">
         <f t="shared" ref="K13:K14" ca="1" si="1">_xlfn.DAYS(H13,$H$6)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L13" s="3">
         <f ca="1">($H$2 - $H$3) / K13</f>
@@ -1340,7 +1355,7 @@
       </c>
       <c r="I14" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J14" s="3">
         <f ca="1">($H$2 - $H$3) / I14</f>
@@ -1348,7 +1363,7 @@
       </c>
       <c r="K14">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L14" s="3">
         <f ca="1">($H$2 - $H$3) / K14</f>
@@ -1458,9 +1473,11 @@
         <v>58</v>
       </c>
       <c r="C22" s="8">
+        <f>SUM(C23:C24)</f>
         <v>12</v>
       </c>
       <c r="D22" s="8">
+        <f>SUM(D23:D24)</f>
         <v>10</v>
       </c>
       <c r="E22" s="17" t="s">
@@ -1500,9 +1517,11 @@
         <v>29</v>
       </c>
       <c r="C25" s="8">
+        <f>SUM(C26:C27)</f>
         <v>10</v>
       </c>
       <c r="D25" s="8">
+        <f>SUM(D26:D27)</f>
         <v>12</v>
       </c>
       <c r="E25" s="17" t="s">
@@ -1542,9 +1561,11 @@
         <v>32</v>
       </c>
       <c r="C28" s="8">
+        <f>SUM(C29:C31)</f>
         <v>5</v>
       </c>
       <c r="D28" s="8">
+        <f>SUM(D29:D31)</f>
         <v>5</v>
       </c>
       <c r="E28" s="17" t="s">
@@ -1598,10 +1619,12 @@
         <v>36</v>
       </c>
       <c r="C32" s="8">
-        <v>7</v>
+        <f>SUM(C33:C41)</f>
+        <v>11</v>
       </c>
       <c r="D32" s="8">
-        <v>7</v>
+        <f>SUM(D33:D41)</f>
+        <v>12</v>
       </c>
       <c r="E32" s="17" t="s">
         <v>54</v>
@@ -1643,7 +1666,7 @@
         <v>1</v>
       </c>
       <c r="D35" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E35" s="16" t="s">
         <v>54</v>
@@ -1654,10 +1677,10 @@
         <v>61</v>
       </c>
       <c r="C36" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D36" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E36" s="16" t="s">
         <v>54</v>
@@ -1671,7 +1694,7 @@
         <v>1</v>
       </c>
       <c r="D37" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="E37" s="16" t="s">
         <v>54</v>
@@ -1707,72 +1730,88 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" s="21" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="C40" s="21">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D40" s="21">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="E40" s="16" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="8" t="s">
+      <c r="B41" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="21">
+        <v>1</v>
+      </c>
+      <c r="D41" s="21">
+        <v>1</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C41" s="8">
-        <v>2</v>
-      </c>
-      <c r="D41" s="8">
-        <v>2</v>
-      </c>
-      <c r="E41" s="17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="42" spans="2:5">
-      <c r="B42" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="7">
-        <v>1</v>
-      </c>
-      <c r="D42" s="7">
-        <v>1</v>
-      </c>
-      <c r="E42" s="16" t="s">
+      <c r="C42" s="8">
+        <f>SUM(C43:C44)</f>
+        <v>2</v>
+      </c>
+      <c r="D42" s="8">
+        <f>SUM(D43:D44)</f>
+        <v>2</v>
+      </c>
+      <c r="E42" s="17" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="43" spans="2:5">
       <c r="B43" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C43" s="7">
+        <v>1</v>
+      </c>
+      <c r="D43" s="7">
+        <v>1</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="C43" s="7">
-        <v>1</v>
-      </c>
-      <c r="D43" s="7">
-        <v>1</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="44" spans="2:5">
-      <c r="B44" s="8" t="s">
+      <c r="C44" s="7">
+        <v>1</v>
+      </c>
+      <c r="D44" s="7">
+        <v>1</v>
+      </c>
+      <c r="E44" s="19" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="8"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="8" t="s">
+      <c r="C45" s="8"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="8" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="2:5">
-      <c r="D45" s="15"/>
+    <row r="46" spans="2:5">
+      <c r="D46" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1805,26 +1844,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100914457C4DEF6B04C80335F04D9CFE9B8" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="384833ccc4364158daff1dfa93252050">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="42b7366e-3919-4bb8-9917-4115af4f71f0" xmlns:ns3="3fed6739-56b2-4f96-bdeb-921328dde709" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8d3663068ba8e99c0b99c921911a4360" ns2:_="" ns3:_="">
     <xsd:import namespace="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
@@ -2059,10 +2078,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3fed6739-56b2-4f96-bdeb-921328dde709" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="42b7366e-3919-4bb8-9917-4115af4f71f0">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
+    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2079,20 +2129,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8EA044FE-1970-4C5E-9C63-D8FEC9524EE6}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393EE603-C983-481A-9007-FE0C7A6F709A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="42b7366e-3919-4bb8-9917-4115af4f71f0"/>
-    <ds:schemaRef ds:uri="3fed6739-56b2-4f96-bdeb-921328dde709"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>